--- a/outputs/evaluation/requirement/validation/gemini-3-1-flash-lite/CF_M04/CF_M04_req_eval_avg.xlsx
+++ b/outputs/evaluation/requirement/validation/gemini-3-1-flash-lite/CF_M04/CF_M04_req_eval_avg.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D22"/>
+  <dimension ref="A1:E22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -526,6 +526,11 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
+          <t>f1</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
           <t>mean semantic meaning</t>
         </is>
       </c>
@@ -543,6 +548,9 @@
         <v>0.7895</v>
       </c>
       <c r="D13" t="n">
+        <v>0.8602</v>
+      </c>
+      <c r="E13" t="n">
         <v>0.9675</v>
       </c>
     </row>
